--- a/National_Retail_Fuel_ReportT.xlsx
+++ b/National_Retail_Fuel_ReportT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5811452E-494B-4BB0-834C-E20140F7C517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D40AE3-29B0-46F4-BF10-75C95F935783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9EE11ED-62AE-4A0D-8441-F310DF0659D3}"/>
   </bookViews>
@@ -22,9 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
-    <t>Geographic Region</t>
-  </si>
-  <si>
     <t>Retail Fuel Brand</t>
   </si>
   <si>
@@ -83,6 +80,9 @@
   </si>
   <si>
     <t>Nissan Motor Co</t>
+  </si>
+  <si>
+    <t>Region</t>
   </si>
 </sst>
 </file>
@@ -887,7 +887,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8FF94B11-B27F-40A8-B341-3D110F172B23}" name="Table1" displayName="Table1" ref="A1:E13" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A1:E13" xr:uid="{8FF94B11-B27F-40A8-B341-3D110F172B23}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F7D5392E-5186-47D8-8D34-0918CE3DA6BE}" name="Geographic Region" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{F7D5392E-5186-47D8-8D34-0918CE3DA6BE}" name="Region" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{49D4F518-DF73-42B1-A42E-520A6651501C}" name="Retail Fuel Brand" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{7C0D5D72-1E11-41AF-AE4F-644AC059C33D}" name="Active Store Footprint Count" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{AF82E1E1-26D5-4B99-8FD1-6D6B28821C0B}" name="Average Unit Cost (MSRP)" dataDxfId="1"/>
@@ -1226,27 +1226,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="C2" s="1">
         <v>36448246</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1">
         <v>32971705</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C4" s="1">
         <v>32751775</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1">
         <v>32063260</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>32443716</v>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1">
         <v>31822170</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C8" s="1">
         <v>32880396</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="1">
         <v>31853081</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1">
         <v>31460870</v>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1">
         <v>32202276</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1">
         <v>31532498</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="9">
         <v>29925570</v>

--- a/National_Retail_Fuel_ReportT.xlsx
+++ b/National_Retail_Fuel_ReportT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D40AE3-29B0-46F4-BF10-75C95F935783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF6CCF4-B75B-445B-9B1A-408221D65CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B9EE11ED-62AE-4A0D-8441-F310DF0659D3}"/>
   </bookViews>
@@ -22,9 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
-    <t>Retail Fuel Brand</t>
-  </si>
-  <si>
     <t>Active Store Footprint Count</t>
   </si>
   <si>
@@ -83,6 +80,9 @@
   </si>
   <si>
     <t>Region</t>
+  </si>
+  <si>
+    <t>Retailer</t>
   </si>
 </sst>
 </file>
@@ -888,7 +888,7 @@
   <autoFilter ref="A1:E13" xr:uid="{8FF94B11-B27F-40A8-B341-3D110F172B23}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F7D5392E-5186-47D8-8D34-0918CE3DA6BE}" name="Region" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{49D4F518-DF73-42B1-A42E-520A6651501C}" name="Retail Fuel Brand" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{49D4F518-DF73-42B1-A42E-520A6651501C}" name="Retailer" dataDxfId="3"/>
     <tableColumn id="3" xr3:uid="{7C0D5D72-1E11-41AF-AE4F-644AC059C33D}" name="Active Store Footprint Count" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{AF82E1E1-26D5-4B99-8FD1-6D6B28821C0B}" name="Average Unit Cost (MSRP)" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{1A0D56C2-0E95-4A74-980C-14FE16D6AE43}" name="Allocated Capital Expenditure (CapEx)" dataDxfId="0"/>
@@ -1226,27 +1226,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>2</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="C2" s="1">
         <v>36448246</v>
@@ -1260,10 +1260,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="C3" s="1">
         <v>32971705</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C4" s="1">
         <v>32751775</v>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1">
         <v>32063260</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1">
         <v>32443716</v>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1">
         <v>31822170</v>
@@ -1345,10 +1345,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C8" s="1">
         <v>32880396</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1">
         <v>31853081</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="1">
         <v>31460870</v>
@@ -1396,10 +1396,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1">
         <v>32202276</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1">
         <v>31532498</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="9">
         <v>29925570</v>
